--- a/artfynd/A 22461-2021 artfynd.xlsx
+++ b/artfynd/A 22461-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 22461-2021 artfynd.xlsx
+++ b/artfynd/A 22461-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1009,6 +1009,858 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>124845231</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>484407</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6850989</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>124844184</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>484126</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6851029</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>124842112</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>484153</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6851068</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>124842678</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57942</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>484059</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6850999</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>124844248</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>484125</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6851025</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>124842177</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>484147</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6851054</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>124844096</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>484126</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6851003</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>124842566</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>484120</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6851027</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22461-2021 artfynd.xlsx
+++ b/artfynd/A 22461-2021 artfynd.xlsx
@@ -1011,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124845231</v>
+        <v>124842112</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1044,26 +1044,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>484407</v>
+        <v>484153</v>
       </c>
       <c r="R5" t="n">
-        <v>6850989</v>
+        <v>6851068</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1233,7 +1224,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124842112</v>
+        <v>124842566</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1266,17 +1257,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>484153</v>
+        <v>484120</v>
       </c>
       <c r="R7" t="n">
-        <v>6851068</v>
+        <v>6851027</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124842678</v>
+        <v>124845231</v>
       </c>
       <c r="B8" t="n">
-        <v>57942</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,41 +1347,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103001</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>484059</v>
+        <v>484407</v>
       </c>
       <c r="R8" t="n">
-        <v>6850999</v>
+        <v>6850989</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1437,10 +1446,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124844248</v>
+        <v>124842678</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>57942</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,50 +1458,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>103001</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>484125</v>
+        <v>484059</v>
       </c>
       <c r="R9" t="n">
-        <v>6851025</v>
+        <v>6850999</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124842177</v>
+        <v>124844096</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1560,25 +1560,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1588,13 +1588,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>484147</v>
+        <v>484126</v>
       </c>
       <c r="R10" t="n">
-        <v>6851054</v>
+        <v>6851003</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1650,10 +1650,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124844096</v>
+        <v>124842177</v>
       </c>
       <c r="B11" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1662,25 +1662,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1690,13 +1690,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>484126</v>
+        <v>484147</v>
       </c>
       <c r="R11" t="n">
-        <v>6851003</v>
+        <v>6851054</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124842566</v>
+        <v>124844248</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1787,7 +1787,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1801,10 +1801,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>484120</v>
+        <v>484125</v>
       </c>
       <c r="R12" t="n">
-        <v>6851027</v>
+        <v>6851025</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 22461-2021 artfynd.xlsx
+++ b/artfynd/A 22461-2021 artfynd.xlsx
@@ -1011,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124842112</v>
+        <v>124844248</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1044,17 +1044,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>484153</v>
+        <v>484125</v>
       </c>
       <c r="R5" t="n">
-        <v>6851068</v>
+        <v>6851025</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124844184</v>
+        <v>124842678</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>57942</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1125,50 +1134,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103001</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>484126</v>
+        <v>484059</v>
       </c>
       <c r="R6" t="n">
-        <v>6851029</v>
+        <v>6850999</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124842566</v>
+        <v>124842177</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1257,26 +1257,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>484120</v>
+        <v>484147</v>
       </c>
       <c r="R7" t="n">
-        <v>6851027</v>
+        <v>6851054</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,10 +1326,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124845231</v>
+        <v>124844096</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,50 +1338,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>484407</v>
+        <v>484126</v>
       </c>
       <c r="R8" t="n">
-        <v>6850989</v>
+        <v>6851003</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1446,10 +1428,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124842678</v>
+        <v>124844184</v>
       </c>
       <c r="B9" t="n">
-        <v>57942</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1458,41 +1440,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103001</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>484059</v>
+        <v>484126</v>
       </c>
       <c r="R9" t="n">
-        <v>6850999</v>
+        <v>6851029</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1548,10 +1539,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124844096</v>
+        <v>124842112</v>
       </c>
       <c r="B10" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1560,25 +1551,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1588,13 +1579,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>484126</v>
+        <v>484153</v>
       </c>
       <c r="R10" t="n">
-        <v>6851003</v>
+        <v>6851068</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1650,7 +1641,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124842177</v>
+        <v>124845231</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1683,17 +1674,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>484147</v>
+        <v>484407</v>
       </c>
       <c r="R11" t="n">
-        <v>6851054</v>
+        <v>6850989</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1752,7 +1752,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124844248</v>
+        <v>124842566</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1787,7 +1787,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1801,10 +1801,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>484125</v>
+        <v>484120</v>
       </c>
       <c r="R12" t="n">
-        <v>6851025</v>
+        <v>6851027</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 22461-2021 artfynd.xlsx
+++ b/artfynd/A 22461-2021 artfynd.xlsx
@@ -1011,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124844248</v>
+        <v>124842112</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1044,26 +1044,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>484125</v>
+        <v>484153</v>
       </c>
       <c r="R5" t="n">
-        <v>6851025</v>
+        <v>6851068</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124842678</v>
+        <v>124844096</v>
       </c>
       <c r="B6" t="n">
-        <v>57942</v>
+        <v>79891</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,21 +1129,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103001</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1162,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>484059</v>
+        <v>484126</v>
       </c>
       <c r="R6" t="n">
-        <v>6850999</v>
+        <v>6851003</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1326,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124844096</v>
+        <v>124844248</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1338,41 +1329,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>484126</v>
+        <v>484125</v>
       </c>
       <c r="R8" t="n">
-        <v>6851003</v>
+        <v>6851025</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124844184</v>
+        <v>124842566</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1477,10 +1477,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>484126</v>
+        <v>484120</v>
       </c>
       <c r="R9" t="n">
-        <v>6851029</v>
+        <v>6851027</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1539,7 +1539,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124842112</v>
+        <v>124845231</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1572,17 +1572,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>484153</v>
+        <v>484407</v>
       </c>
       <c r="R10" t="n">
-        <v>6851068</v>
+        <v>6850989</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1650,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124845231</v>
+        <v>124844184</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1676,7 +1685,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1690,10 +1699,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>484407</v>
+        <v>484126</v>
       </c>
       <c r="R11" t="n">
-        <v>6850989</v>
+        <v>6851029</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1752,10 +1761,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124842566</v>
+        <v>124842678</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>57942</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1764,50 +1773,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>103001</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>484120</v>
+        <v>484059</v>
       </c>
       <c r="R12" t="n">
-        <v>6851027</v>
+        <v>6850999</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>

--- a/artfynd/A 22461-2021 artfynd.xlsx
+++ b/artfynd/A 22461-2021 artfynd.xlsx
@@ -1011,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124842112</v>
+        <v>124845231</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1044,17 +1044,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>484153</v>
+        <v>484407</v>
       </c>
       <c r="R5" t="n">
-        <v>6851068</v>
+        <v>6850989</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124844096</v>
+        <v>124842177</v>
       </c>
       <c r="B6" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1125,25 +1134,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,13 +1162,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>484126</v>
+        <v>484147</v>
       </c>
       <c r="R6" t="n">
-        <v>6851003</v>
+        <v>6851054</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1215,10 +1224,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124842177</v>
+        <v>124842678</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>57942</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1227,25 +1236,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>103001</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,13 +1264,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>484147</v>
+        <v>484059</v>
       </c>
       <c r="R7" t="n">
-        <v>6851054</v>
+        <v>6850999</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1317,10 +1326,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124844248</v>
+        <v>124844096</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1329,50 +1338,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>484125</v>
+        <v>484126</v>
       </c>
       <c r="R8" t="n">
-        <v>6851025</v>
+        <v>6851003</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124845231</v>
+        <v>124842112</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1572,26 +1572,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>484407</v>
+        <v>484153</v>
       </c>
       <c r="R10" t="n">
-        <v>6850989</v>
+        <v>6851068</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1761,10 +1752,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124842678</v>
+        <v>124844248</v>
       </c>
       <c r="B12" t="n">
-        <v>57942</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1773,41 +1764,50 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103001</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>484059</v>
+        <v>484125</v>
       </c>
       <c r="R12" t="n">
-        <v>6850999</v>
+        <v>6851025</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>

--- a/artfynd/A 22461-2021 artfynd.xlsx
+++ b/artfynd/A 22461-2021 artfynd.xlsx
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124845231</v>
+        <v>124842678</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>57942</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,50 +1023,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>103001</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>484407</v>
+        <v>484059</v>
       </c>
       <c r="R5" t="n">
-        <v>6850989</v>
+        <v>6850999</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1122,7 +1113,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124842177</v>
+        <v>124845231</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1155,17 +1146,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>484147</v>
+        <v>484407</v>
       </c>
       <c r="R6" t="n">
-        <v>6851054</v>
+        <v>6850989</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1224,10 +1224,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124842678</v>
+        <v>124842177</v>
       </c>
       <c r="B7" t="n">
-        <v>57942</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1236,25 +1236,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103001</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1264,13 +1264,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>484059</v>
+        <v>484147</v>
       </c>
       <c r="R7" t="n">
-        <v>6850999</v>
+        <v>6851054</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124842566</v>
+        <v>124842112</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1461,26 +1461,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>484120</v>
+        <v>484153</v>
       </c>
       <c r="R9" t="n">
-        <v>6851027</v>
+        <v>6851068</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1539,7 +1530,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124842112</v>
+        <v>124844184</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1572,17 +1563,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>484153</v>
+        <v>484126</v>
       </c>
       <c r="R10" t="n">
-        <v>6851068</v>
+        <v>6851029</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1641,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124844184</v>
+        <v>124842566</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>484126</v>
+        <v>484120</v>
       </c>
       <c r="R11" t="n">
-        <v>6851029</v>
+        <v>6851027</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 22461-2021 artfynd.xlsx
+++ b/artfynd/A 22461-2021 artfynd.xlsx
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124842678</v>
+        <v>124842177</v>
       </c>
       <c r="B5" t="n">
-        <v>57942</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103001</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,13 +1051,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>484059</v>
+        <v>484147</v>
       </c>
       <c r="R5" t="n">
-        <v>6850999</v>
+        <v>6851054</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124845231</v>
+        <v>124842112</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1146,26 +1146,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>484407</v>
+        <v>484153</v>
       </c>
       <c r="R6" t="n">
-        <v>6850989</v>
+        <v>6851068</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1224,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124842177</v>
+        <v>124842678</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>57942</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1236,25 +1227,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>103001</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1264,13 +1255,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>484147</v>
+        <v>484059</v>
       </c>
       <c r="R7" t="n">
-        <v>6851054</v>
+        <v>6850999</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1326,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124844096</v>
+        <v>124844184</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1338,28 +1329,37 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
@@ -1369,10 +1369,10 @@
         <v>484126</v>
       </c>
       <c r="R8" t="n">
-        <v>6851003</v>
+        <v>6851029</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124842112</v>
+        <v>124842566</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1461,17 +1461,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>484153</v>
+        <v>484120</v>
       </c>
       <c r="R9" t="n">
-        <v>6851068</v>
+        <v>6851027</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1530,10 +1539,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124844184</v>
+        <v>124844096</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1542,37 +1551,28 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
@@ -1582,10 +1582,10 @@
         <v>484126</v>
       </c>
       <c r="R10" t="n">
-        <v>6851029</v>
+        <v>6851003</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124842566</v>
+        <v>124845231</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>484120</v>
+        <v>484407</v>
       </c>
       <c r="R11" t="n">
-        <v>6851027</v>
+        <v>6850989</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 22461-2021 artfynd.xlsx
+++ b/artfynd/A 22461-2021 artfynd.xlsx
@@ -1215,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124842678</v>
+        <v>124844184</v>
       </c>
       <c r="B7" t="n">
-        <v>57942</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1227,41 +1227,50 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103001</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>484059</v>
+        <v>484126</v>
       </c>
       <c r="R7" t="n">
-        <v>6850999</v>
+        <v>6851029</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1317,7 +1326,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124844184</v>
+        <v>124842566</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1366,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>484126</v>
+        <v>484120</v>
       </c>
       <c r="R8" t="n">
-        <v>6851029</v>
+        <v>6851027</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1428,10 +1437,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124842566</v>
+        <v>124842678</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>57942</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1440,50 +1449,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>103001</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>484120</v>
+        <v>484059</v>
       </c>
       <c r="R9" t="n">
-        <v>6851027</v>
+        <v>6850999</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>

--- a/artfynd/A 22461-2021 artfynd.xlsx
+++ b/artfynd/A 22461-2021 artfynd.xlsx
@@ -1011,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124842177</v>
+        <v>124845231</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1044,17 +1044,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>484147</v>
+        <v>484407</v>
       </c>
       <c r="R5" t="n">
-        <v>6851054</v>
+        <v>6850989</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,7 +1122,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124842112</v>
+        <v>124842177</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1153,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>484153</v>
+        <v>484147</v>
       </c>
       <c r="R6" t="n">
-        <v>6851068</v>
+        <v>6851054</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,7 +1224,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124844184</v>
+        <v>124842566</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1264,10 +1273,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>484126</v>
+        <v>484120</v>
       </c>
       <c r="R7" t="n">
-        <v>6851029</v>
+        <v>6851027</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1326,10 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124842566</v>
+        <v>124842678</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>57942</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1338,50 +1347,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>103001</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>484120</v>
+        <v>484059</v>
       </c>
       <c r="R8" t="n">
-        <v>6851027</v>
+        <v>6850999</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1437,10 +1437,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124842678</v>
+        <v>124844096</v>
       </c>
       <c r="B9" t="n">
-        <v>57942</v>
+        <v>79891</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1453,21 +1453,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103001</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1477,10 +1477,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>484059</v>
+        <v>484126</v>
       </c>
       <c r="R9" t="n">
-        <v>6850999</v>
+        <v>6851003</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1539,10 +1539,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124844096</v>
+        <v>124844248</v>
       </c>
       <c r="B10" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1551,41 +1551,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>484126</v>
+        <v>484125</v>
       </c>
       <c r="R10" t="n">
-        <v>6851003</v>
+        <v>6851025</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1641,7 +1650,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124845231</v>
+        <v>124844184</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1676,7 +1685,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1690,10 +1699,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>484407</v>
+        <v>484126</v>
       </c>
       <c r="R11" t="n">
-        <v>6850989</v>
+        <v>6851029</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1752,7 +1761,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124844248</v>
+        <v>124842112</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1785,26 +1794,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>484125</v>
+        <v>484153</v>
       </c>
       <c r="R12" t="n">
-        <v>6851025</v>
+        <v>6851068</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 22461-2021 artfynd.xlsx
+++ b/artfynd/A 22461-2021 artfynd.xlsx
@@ -1011,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124845231</v>
+        <v>124842112</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1044,26 +1044,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>484407</v>
+        <v>484153</v>
       </c>
       <c r="R5" t="n">
-        <v>6850989</v>
+        <v>6851068</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1224,7 +1215,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124842566</v>
+        <v>124844184</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1273,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>484120</v>
+        <v>484126</v>
       </c>
       <c r="R7" t="n">
-        <v>6851027</v>
+        <v>6851029</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,10 +1326,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124842678</v>
+        <v>124845231</v>
       </c>
       <c r="B8" t="n">
-        <v>57942</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,41 +1338,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103001</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>484059</v>
+        <v>484407</v>
       </c>
       <c r="R8" t="n">
-        <v>6850999</v>
+        <v>6850989</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1437,10 +1437,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124844096</v>
+        <v>124842566</v>
       </c>
       <c r="B9" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,41 +1449,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>484126</v>
+        <v>484120</v>
       </c>
       <c r="R9" t="n">
-        <v>6851003</v>
+        <v>6851027</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1650,10 +1659,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124844184</v>
+        <v>124844096</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1662,37 +1671,28 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
@@ -1702,10 +1702,10 @@
         <v>484126</v>
       </c>
       <c r="R11" t="n">
-        <v>6851029</v>
+        <v>6851003</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1761,10 +1761,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124842112</v>
+        <v>124842678</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>57942</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1773,25 +1773,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>103001</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1801,13 +1801,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>484153</v>
+        <v>484059</v>
       </c>
       <c r="R12" t="n">
-        <v>6851068</v>
+        <v>6850999</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>

--- a/artfynd/A 22461-2021 artfynd.xlsx
+++ b/artfynd/A 22461-2021 artfynd.xlsx
@@ -1113,7 +1113,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124842177</v>
+        <v>124844248</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1146,17 +1146,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>484147</v>
+        <v>484125</v>
       </c>
       <c r="R6" t="n">
-        <v>6851054</v>
+        <v>6851025</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1326,10 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124845231</v>
+        <v>124844096</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1338,50 +1347,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>484407</v>
+        <v>484126</v>
       </c>
       <c r="R8" t="n">
-        <v>6850989</v>
+        <v>6851003</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124842566</v>
+        <v>124842177</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1470,26 +1470,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>484120</v>
+        <v>484147</v>
       </c>
       <c r="R9" t="n">
-        <v>6851027</v>
+        <v>6851054</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1548,7 +1539,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124844248</v>
+        <v>124842566</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1583,7 +1574,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1597,10 +1588,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>484125</v>
+        <v>484120</v>
       </c>
       <c r="R10" t="n">
-        <v>6851025</v>
+        <v>6851027</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1659,10 +1650,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124844096</v>
+        <v>124845231</v>
       </c>
       <c r="B11" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1671,41 +1662,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>484126</v>
+        <v>484407</v>
       </c>
       <c r="R11" t="n">
-        <v>6851003</v>
+        <v>6850989</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>

--- a/artfynd/A 22461-2021 artfynd.xlsx
+++ b/artfynd/A 22461-2021 artfynd.xlsx
@@ -1011,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124842112</v>
+        <v>124844248</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1044,17 +1044,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>484153</v>
+        <v>484125</v>
       </c>
       <c r="R5" t="n">
-        <v>6851068</v>
+        <v>6851025</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,7 +1122,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124844248</v>
+        <v>124842112</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1146,26 +1155,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>484125</v>
+        <v>484153</v>
       </c>
       <c r="R6" t="n">
-        <v>6851025</v>
+        <v>6851068</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1224,7 +1224,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124844184</v>
+        <v>124842566</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1273,10 +1273,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>484126</v>
+        <v>484120</v>
       </c>
       <c r="R7" t="n">
-        <v>6851029</v>
+        <v>6851027</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1539,10 +1539,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124842566</v>
+        <v>124842678</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>57942</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1551,50 +1551,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>103001</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>484120</v>
+        <v>484059</v>
       </c>
       <c r="R10" t="n">
-        <v>6851027</v>
+        <v>6850999</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1761,10 +1752,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124842678</v>
+        <v>124844184</v>
       </c>
       <c r="B12" t="n">
-        <v>57942</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1773,41 +1764,50 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103001</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>484059</v>
+        <v>484126</v>
       </c>
       <c r="R12" t="n">
-        <v>6850999</v>
+        <v>6851029</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>

--- a/artfynd/A 22461-2021 artfynd.xlsx
+++ b/artfynd/A 22461-2021 artfynd.xlsx
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124844248</v>
+        <v>124844096</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,50 +1023,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>484125</v>
+        <v>484126</v>
       </c>
       <c r="R5" t="n">
-        <v>6851025</v>
+        <v>6851003</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1122,7 +1113,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124842112</v>
+        <v>124844248</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1155,17 +1146,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>484153</v>
+        <v>484125</v>
       </c>
       <c r="R6" t="n">
-        <v>6851068</v>
+        <v>6851025</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1224,7 +1224,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124842566</v>
+        <v>124844184</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1273,10 +1273,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>484120</v>
+        <v>484126</v>
       </c>
       <c r="R7" t="n">
-        <v>6851027</v>
+        <v>6851029</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124844096</v>
+        <v>124842678</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
+        <v>57942</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1351,21 +1351,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>103001</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>484126</v>
+        <v>484059</v>
       </c>
       <c r="R8" t="n">
-        <v>6851003</v>
+        <v>6850999</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1437,7 +1437,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124842177</v>
+        <v>124842566</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1470,17 +1470,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>484147</v>
+        <v>484120</v>
       </c>
       <c r="R9" t="n">
-        <v>6851054</v>
+        <v>6851027</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1539,10 +1548,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124842678</v>
+        <v>124842177</v>
       </c>
       <c r="B10" t="n">
-        <v>57942</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1551,25 +1560,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103001</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1579,13 +1588,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>484059</v>
+        <v>484147</v>
       </c>
       <c r="R10" t="n">
-        <v>6850999</v>
+        <v>6851054</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1752,7 +1761,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124844184</v>
+        <v>124842112</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1785,26 +1794,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>484126</v>
+        <v>484153</v>
       </c>
       <c r="R12" t="n">
-        <v>6851029</v>
+        <v>6851068</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 22461-2021 artfynd.xlsx
+++ b/artfynd/A 22461-2021 artfynd.xlsx
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124844096</v>
+        <v>124845231</v>
       </c>
       <c r="B5" t="n">
-        <v>79891</v>
+        <v>98269</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,41 +1023,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>484126</v>
+        <v>484407</v>
       </c>
       <c r="R5" t="n">
-        <v>6851003</v>
+        <v>6850989</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1113,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124844248</v>
+        <v>124844096</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>80028</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1125,50 +1134,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>484125</v>
+        <v>484126</v>
       </c>
       <c r="R6" t="n">
-        <v>6851025</v>
+        <v>6851003</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>124844184</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124842678</v>
+        <v>124842566</v>
       </c>
       <c r="B8" t="n">
-        <v>57942</v>
+        <v>98269</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,41 +1347,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103001</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>484059</v>
+        <v>484120</v>
       </c>
       <c r="R8" t="n">
-        <v>6850999</v>
+        <v>6851027</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1437,10 +1446,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124842566</v>
+        <v>124842678</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>58060</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,50 +1458,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>103001</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>484120</v>
+        <v>484059</v>
       </c>
       <c r="R9" t="n">
-        <v>6851027</v>
+        <v>6850999</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124842177</v>
+        <v>124844248</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1581,17 +1581,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>484147</v>
+        <v>484125</v>
       </c>
       <c r="R10" t="n">
-        <v>6851054</v>
+        <v>6851025</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1650,10 +1659,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124845231</v>
+        <v>124842112</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1683,26 +1692,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>484407</v>
+        <v>484153</v>
       </c>
       <c r="R11" t="n">
-        <v>6850989</v>
+        <v>6851068</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1761,10 +1761,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124842112</v>
+        <v>124842177</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1801,10 +1801,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>484153</v>
+        <v>484147</v>
       </c>
       <c r="R12" t="n">
-        <v>6851068</v>
+        <v>6851054</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 22461-2021 artfynd.xlsx
+++ b/artfynd/A 22461-2021 artfynd.xlsx
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124845231</v>
+        <v>124844096</v>
       </c>
       <c r="B5" t="n">
-        <v>98269</v>
+        <v>80028</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,50 +1023,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>484407</v>
+        <v>484126</v>
       </c>
       <c r="R5" t="n">
-        <v>6850989</v>
+        <v>6851003</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1122,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124844096</v>
+        <v>124845231</v>
       </c>
       <c r="B6" t="n">
-        <v>80028</v>
+        <v>98269</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,41 +1125,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Näveråsens naturreservat, Näveråsens naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>484126</v>
+        <v>484407</v>
       </c>
       <c r="R6" t="n">
-        <v>6851003</v>
+        <v>6850989</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
